--- a/themes/theme-0/plitki-navigatora.xlsx
+++ b/themes/theme-0/plitki-navigatora.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="100">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -270,18 +270,6 @@
     <t xml:space="preserve">бьют или угрожают сейчас</t>
   </si>
   <si>
-    <t xml:space="preserve">Предстоит</t>
-  </si>
-  <si>
-    <t xml:space="preserve">поездка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лечение зуба</t>
-  </si>
-  <si>
-    <t xml:space="preserve">работа</t>
-  </si>
-  <si>
     <t xml:space="preserve">Плитка или подгруппа</t>
   </si>
   <si>
@@ -336,7 +324,7 @@
     <t xml:space="preserve">Статус</t>
   </si>
   <si>
-    <t xml:space="preserve">Предложение от 20.10.2026, пользователем не утверждено.</t>
+    <t xml:space="preserve">Утверждено пользователем 20.10.2026 с правками: 15 плиток одного уровня (группа «Предстоит» снята), список скрыт до выбора группы.</t>
   </si>
 </sst>
 </file>
@@ -448,8 +436,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -461,15 +453,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -482,7 +474,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -494,6 +486,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -757,1066 +757,1018 @@
   <dimension ref="A1:E62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+    <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+    <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="D40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="B41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="B42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="B43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="B44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="B45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="B47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="B48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="B49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="B50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="B51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="B52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="B53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="B54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="B55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" s="2" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="B57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="B58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="B59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:E62"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1838,224 +1790,213 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A2)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A3)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A4)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A5)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A6)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A8)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A9)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A10)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A11)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A12)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A13)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A14)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="B16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A16)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A17)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="n">
-        <f aca="false">SUM(C2:C17)</f>
-        <v>61</v>
-      </c>
-    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="n">
+        <f aca="false">SUM(C2:C16)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2075,72 +2016,72 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="80"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/themes/theme-0/plitki-navigatora.xlsx
+++ b/themes/theme-0/plitki-navigatora.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="102">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t xml:space="preserve">Кожа и аллергия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пожелтели кожа или белки глаз</t>
   </si>
   <si>
     <t xml:space="preserve">зуд</t>
@@ -1335,13 +1338,13 @@
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1352,7 +1355,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>7</v>
@@ -1369,7 +1372,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>7</v>
@@ -1386,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>7</v>
@@ -1403,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>7</v>
@@ -1420,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1437,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>7</v>
@@ -1454,7 +1457,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>7</v>
@@ -1468,16 +1471,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1485,13 +1488,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>59</v>
@@ -1502,13 +1505,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>60</v>
@@ -1519,16 +1522,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1536,13 +1539,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
@@ -1553,13 +1556,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>64</v>
@@ -1570,13 +1573,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>65</v>
@@ -1587,13 +1590,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>66</v>
@@ -1604,16 +1607,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1621,13 +1624,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>69</v>
@@ -1638,13 +1641,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>70</v>
@@ -1655,13 +1658,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>71</v>
@@ -1672,16 +1675,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1689,13 +1692,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>74</v>
@@ -1706,13 +1709,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>75</v>
@@ -1723,13 +1726,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>76</v>
@@ -1740,16 +1743,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1757,16 +1760,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1774,19 +1777,35 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:E62"/>
@@ -1816,13 +1835,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1906,12 +1925,12 @@
       </c>
       <c r="C8" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$C$2:$C$62,A8)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>5</v>
@@ -1923,7 +1942,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>5</v>
@@ -1935,10 +1954,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A11)</f>
@@ -1947,10 +1966,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A12)</f>
@@ -1959,10 +1978,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A13)</f>
@@ -1971,10 +1990,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A14)</f>
@@ -1983,10 +2002,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A15)</f>
@@ -1995,10 +2014,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="5" t="n">
         <f aca="false">COUNTIFS(Карточки!$D$2:$D$62,A16)</f>
@@ -2007,12 +2026,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="n">
         <f aca="false">SUM(C2:C16)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2041,66 +2060,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
